--- a/untranslated/downloads/data-excel/5.4.1.xlsx
+++ b/untranslated/downloads/data-excel/5.4.1.xlsx
@@ -595,7 +595,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -612,7 +612,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
@@ -629,7 +629,7 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -646,7 +646,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>27</v>
       </c>
@@ -663,7 +663,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
@@ -680,7 +680,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>9</v>
       </c>
@@ -697,7 +697,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -714,7 +714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>24</v>
       </c>
@@ -731,7 +731,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>27</v>
       </c>
@@ -748,7 +748,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
@@ -765,7 +765,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
@@ -782,7 +782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>21</v>
       </c>
@@ -799,7 +799,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -816,7 +816,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>27</v>
       </c>
@@ -833,7 +833,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>30</v>
       </c>
@@ -850,7 +850,7 @@
         <v>2.8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>15</v>
       </c>
@@ -867,7 +867,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
@@ -884,7 +884,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>24</v>
       </c>
@@ -901,7 +901,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>27</v>
       </c>
@@ -918,7 +918,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="12.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>30</v>
       </c>
